--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="43" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>365짐 천안두정점</t>
+          <t>퓨처휘트니스 성성점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>365gymdj@naver.com</t>
+          <t>futurefit_ss@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1391-3657</t>
+          <t>0507-1330-3335</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 1공단1길 52 센트하임 2층 365짐</t>
+          <t>충청남도 천안시 서북구 성성5로 113 B1층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://litt.ly/365gym</t>
+          <t>https://blog.naver.com/futurefit_ss</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4134</v>
+        <v>920</v>
       </c>
       <c r="Q2" t="n">
-        <v>2944</v>
+        <v>837</v>
       </c>
       <c r="R2" t="n">
-        <v>7078</v>
+        <v>1757</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1490379364</t>
+          <t>1174227079</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1490379364</t>
+          <t>https://m.place.naver.com/place/1174227079</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>퓨처휘트니스 성성점 헬스&amp;PT</t>
+          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>futurefit_ss@naver.com</t>
+          <t>miraon2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1330-3335</t>
+          <t>0507-1364-7983</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 성성5로 113 B1층</t>
+          <t>충청남도 천안시 서북구 두정로 228 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/futurefit_ss</t>
+          <t>https://blog.naver.com/miraon2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>920</v>
+        <v>866</v>
       </c>
       <c r="Q3" t="n">
-        <v>837</v>
+        <v>1409</v>
       </c>
       <c r="R3" t="n">
-        <v>1757</v>
+        <v>2275</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1174227079</t>
+          <t>1570105670</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174227079</t>
+          <t>https://m.place.naver.com/place/1570105670</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,39 +747,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>miraon2@naver.com</t>
-        </is>
-      </c>
+          <t>엠티오청당 PT스튜디오</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1364-7983</t>
+          <t>0507-1319-6257</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 두정로 228 2층</t>
+          <t>충청남도 천안시 동남구 남부대로 322 5층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miraon2</t>
+          <t>https://litt.ly/mtofitnessinfo</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -789,7 +785,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -805,17 +801,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>866</v>
+        <v>111</v>
       </c>
       <c r="Q4" t="n">
-        <v>1401</v>
+        <v>462</v>
       </c>
       <c r="R4" t="n">
-        <v>2267</v>
+        <v>573</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +820,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1570105670</t>
+          <t>1142720467</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570105670</t>
+          <t>https://m.place.naver.com/place/1142720467</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,7 +837,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -931,30 +927,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엠티오청당 PT스튜디오</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0507-1319-6257</t>
-        </is>
-      </c>
+          <t>피지오스튜디오 필라테스 &amp; PT 천안 신불당점</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충청남도 천안시 동남구 남부대로 322 5층</t>
+          <t>충청남도 천안시 서북구 불당25로 176 율곡스퀘어 2층 206, 207호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://litt.ly/mtofitnessinfo</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -985,17 +985,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>111</v>
+        <v>415</v>
       </c>
       <c r="Q6" t="n">
-        <v>462</v>
+        <v>685</v>
       </c>
       <c r="R6" t="n">
-        <v>573</v>
+        <v>1100</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1142720467</t>
+          <t>1223842821</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142720467</t>
+          <t>https://m.place.naver.com/place/1223842821</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1021,39 +1021,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 천안 신불당점</t>
+          <t>닥터고 재활운동센터</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>contact@physiostudio.co.kr</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>drkoesc@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1396-9090</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 불당25로 176 율곡스퀘어 2층 206, 207호</t>
+          <t>충청남도 천안시 서북구 백석로 93 5층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.physiostudio.co.kr/</t>
+          <t>https://blog.naver.com/drkoesc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1083,13 +1083,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>415</v>
+        <v>10</v>
       </c>
       <c r="Q7" t="n">
-        <v>685</v>
+        <v>71</v>
       </c>
       <c r="R7" t="n">
-        <v>1100</v>
+        <v>81</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1223842821</t>
+          <t>1236215652</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223842821</t>
+          <t>https://m.place.naver.com/place/1236215652</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1115,34 +1115,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하루운동 PT&amp;헬스 천안두정점</t>
+          <t>느루피트니스 불당점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vhtm56@naver.com</t>
+          <t>fit_neuru@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1368-1126</t>
+          <t>0507-1305-9187</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 두정중2길 4 4층</t>
+          <t>충청남도 천안시 서북구 불당21로 67-8 정석4차 306호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vhtm56</t>
+          <t>https://www.instagram.com/neuru_fitness_official</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>201</v>
+        <v>129</v>
       </c>
       <c r="Q8" t="n">
-        <v>112</v>
+        <v>358</v>
       </c>
       <c r="R8" t="n">
-        <v>313</v>
+        <v>487</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1043441965</t>
+          <t>1295886962</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043441965</t>
+          <t>https://m.place.naver.com/place/1295886962</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1209,34 +1209,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>미녀와야수짐 안서점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>anseo1-1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1309-9270</t>
+          <t>0507-1333-6152</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충청남도 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충청남도 천안시 동남구 안서1길 1 젊은태양빌딩 3층 미녀와야수짐</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/anseo1-1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1271,13 +1271,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>116</v>
+        <v>1486</v>
       </c>
       <c r="Q9" t="n">
-        <v>53</v>
+        <v>250</v>
       </c>
       <c r="R9" t="n">
-        <v>169</v>
+        <v>1736</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1036519698</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1036519698</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1303,61 +1303,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>로라필라테스 불당직영점</t>
+          <t>FE트레이닝센터 천안점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rorapilates@naver.com</t>
+          <t>edengarden0927@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1352-3686</t>
+          <t>0507-1462-2471</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당21로 65 7층 705호</t>
+          <t>충청남도 천안시 서북구 불당25로 236 디엠센텀시티 2층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://m.booking.naver.com/booking/5/bizes/952862</t>
+          <t>https://blog.naver.com/edengarden0927</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w43hyb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>
@@ -1369,13 +1365,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="Q10" t="n">
-        <v>158</v>
+        <v>562</v>
       </c>
       <c r="R10" t="n">
-        <v>429</v>
+        <v>818</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1380,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1526607842</t>
+          <t>1149284242</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1526607842</t>
+          <t>https://m.place.naver.com/place/1149284242</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1401,34 +1397,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공감PT여성전용공간 성정동점</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>djawndud99@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1344-6267</t>
+          <t>0507-1378-6132</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충청남도 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggampt</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1454,7 +1450,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1463,30 +1459,970 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>948</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1115</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1197800655</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1197800655</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>크로스핏 트레이닝그라운드 SWEAT45 &amp; PT 불당점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ddpwwf@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1352-7077</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 불당4로 39-59 1F</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/ddpwwf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>452</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>95</v>
+      </c>
+      <c r="R12" t="n">
+        <v>547</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1128230416</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1128230416</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>핏라이프피트니스 PT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>fitlife-experts@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1333-1224</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 성성8로 2-44 바루나타워 6층, 핏라이프피트니스</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/fitlife-experts</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>620</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1285</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1905</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1310515227</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1310515227</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>천안 쌍용동 헬스&amp;PT 미녀와야수짐</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dabinparks@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0507-1309-2118</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 충무로 167-18 4층 미녀와야수짐 쌍용점</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dabinparks</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>862</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>447</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1309</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1103877507</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1103877507</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>공감PT여성전용공간 성정동점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>djawndud99@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1344-6267</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 성정두정로 38 4층 401호</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/gonggampt</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
         <v>46</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q15" t="n">
         <v>160</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R15" t="n">
         <v>206</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>1159361767</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>하와이짐 직산점</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>duddns20@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1484-8878</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 직산읍 직산로 43 4층 하와이짐</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hawaiigym8877?igsh=eDdxcDRqZ3pjc2I5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>235</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>152</v>
+      </c>
+      <c r="R16" t="n">
+        <v>387</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1303396625</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1303396625</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>핏러너 그룹PT 백석점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>klsmys@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0507-1324-7967</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 한들3로 85-48 1층 101호</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/klsmys</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>150</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>217</v>
+      </c>
+      <c r="R17" t="n">
+        <v>367</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1793060014</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1793060014</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>퓨처휘트니스 청당 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>futurefit@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1457-2391</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 동남구 청수14로 102 에이스법조타워 3층 301~309호</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/futurefit</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>923</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>816</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1739</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1704647072</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1704647072</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>지방부수리 24시 헬스&amp;PT 불당점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>kmgzxcv@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1344-7030</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 검은들1길 26 6층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/kmgzxcv/223855885181</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>1538</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>483</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2021</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1012207514</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1012207514</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>온더짐 천안두정점 헬스 PT 필라테스</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>onthegym_official@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1390-0255</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 서북구 두정로 251 3층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://youtube.com/channel/UCf8AIAmWKIKIzgNsS6vXaQg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>151</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>307</v>
+      </c>
+      <c r="R20" t="n">
+        <v>458</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1233432048</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1233432048</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>오버핏스튜디오</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>overfit_studio@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1373-9636</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>충청남도 천안시 동남구 청수12로 44 301호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/overfit_studio</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>56</v>
+      </c>
+      <c r="R21" t="n">
+        <v>72</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>2083680977</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2083680977</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,39 +559,39 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>퓨처휘트니스 성성점 헬스&amp;PT</t>
+          <t>365짐 천안두정점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>futurefit_ss@naver.com</t>
+          <t>365gymdj@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1330-3335</t>
+          <t>0507-1391-3657</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 성성5로 113 B1층</t>
+          <t>충남 천안시 서북구 1공단1길 52 센트하임 2층 365짐</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/futurefit_ss</t>
+          <t>https://litt.ly/365gym</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4xy9t</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>920</v>
+        <v>4146</v>
       </c>
       <c r="Q2" t="n">
-        <v>837</v>
+        <v>2964</v>
       </c>
       <c r="R2" t="n">
-        <v>1757</v>
+        <v>7110</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,17 +640,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1174227079</t>
+          <t>1490379364</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174227079</t>
+          <t>https://m.place.naver.com/place/1490379364</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -658,34 +662,34 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미라온휘트니스 천안두정점 헬스 PT 필라테스</t>
+          <t>피지오스튜디오 필라테스 &amp; PT 천안 신불당점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>miraon2@naver.com</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0507-1364-7983</t>
-        </is>
-      </c>
+          <t>physiostudio2021@naver.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>contact@physiostudio.co.kr</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 두정로 228 2층</t>
+          <t>충남 천안시 서북구 불당25로 176 율곡스퀘어 2층 206, 207호</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miraon2</t>
+          <t>https://www.physiostudio.co.kr/</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsb8r4z</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>866</v>
+        <v>414</v>
       </c>
       <c r="Q3" t="n">
-        <v>1409</v>
+        <v>689</v>
       </c>
       <c r="R3" t="n">
-        <v>2275</v>
+        <v>1103</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,52 +738,56 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1570105670</t>
+          <t>1223842821</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1570105670</t>
+          <t>https://m.place.naver.com/place/1223842821</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엠티오청당 PT스튜디오</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>퓨처휘트니스 성성점 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>futurefit_ss@naver.com</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1319-6257</t>
+          <t>0507-1330-3335</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충청남도 천안시 동남구 남부대로 322 5층</t>
+          <t>충남 천안시 서북구 성성5로 113 B1층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://litt.ly/mtofitnessinfo</t>
+          <t>https://blog.naver.com/futurefit_ss</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -785,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w489t7</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -801,17 +817,17 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>111</v>
+        <v>924</v>
       </c>
       <c r="Q4" t="n">
-        <v>462</v>
+        <v>838</v>
       </c>
       <c r="R4" t="n">
-        <v>573</v>
+        <v>1762</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -820,47 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1142720467</t>
+          <t>1174227079</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1142720467</t>
+          <t>https://m.place.naver.com/place/1174227079</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미녀와야수짐 헬스&amp;PT 차암점</t>
+          <t>오버핏스튜디오</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>beauty_beast_gym@naver.com</t>
+          <t>overfit_studio@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0507-1373-9636</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 3공단6로 58-8 천안비즈타워 307호~313호</t>
+          <t>충남 천안시 동남구 청수12로 44 301호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_beast_chaam?igsh=bmh0NW9vYWYxN2Vl</t>
+          <t>https://blog.naver.com/overfit_studio</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -875,15 +895,19 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcs5xy4</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -895,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>360</v>
+        <v>14</v>
       </c>
       <c r="Q5" t="n">
-        <v>408</v>
+        <v>58</v>
       </c>
       <c r="R5" t="n">
-        <v>768</v>
+        <v>72</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -910,56 +934,56 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1965484568</t>
+          <t>2083680977</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965484568</t>
+          <t>https://m.place.naver.com/place/2083680977</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>피지오스튜디오 필라테스 &amp; PT 천안 신불당점</t>
+          <t>크로스핏 트레이닝그라운드 SWEAT45 &amp; PT 불당점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>physiostudio2021@naver.com</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>contact@physiostudio.co.kr</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>ddpwwf@naver.com</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0507-1352-7077</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 불당25로 176 율곡스퀘어 2층 206, 207호</t>
+          <t>충남 천안시 서북구 불당4로 39-59 1F</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.physiostudio.co.kr/</t>
+          <t>https://blog.naver.com/ddpwwf</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -974,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w43u70</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -989,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>415</v>
+        <v>455</v>
       </c>
       <c r="Q6" t="n">
-        <v>685</v>
+        <v>95</v>
       </c>
       <c r="R6" t="n">
-        <v>1100</v>
+        <v>550</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1004,51 +1032,47 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1223842821</t>
+          <t>1128230416</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1223842821</t>
+          <t>https://m.place.naver.com/place/1128230416</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>닥터고 재활운동센터</t>
+          <t>미녀와야수짐 헬스&amp;PT 차암점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>drkoesc@naver.com</t>
+          <t>beauty_beast_gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1396-9090</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 백석로 93 5층</t>
+          <t>충남 천안시 서북구 3공단6로 58-8 천안비즈타워 307호~313호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/drkoesc</t>
+          <t>https://www.instagram.com/beauty_beast_chaam?igsh=bmh0NW9vYWYxN2Vl</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1063,15 +1087,19 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5zg2w</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1083,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>360</v>
       </c>
       <c r="Q7" t="n">
-        <v>71</v>
+        <v>408</v>
       </c>
       <c r="R7" t="n">
-        <v>81</v>
+        <v>768</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1098,51 +1126,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1236215652</t>
+          <t>1965484568</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236215652</t>
+          <t>https://m.place.naver.com/place/1965484568</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>느루피트니스 불당점</t>
+          <t>365일 24시 짐그로우 쌍용역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fit_neuru@naver.com</t>
+          <t>gymgrow@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1305-9187</t>
+          <t>0507-1465-3657</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 불당21로 67-8 정석4차 306호</t>
+          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/neuru_fitness_official</t>
+          <t>https://blog.naver.com/gymgrow/223761915716</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1157,15 +1185,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w7k9</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1177,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>129</v>
+        <v>513</v>
       </c>
       <c r="Q8" t="n">
-        <v>358</v>
+        <v>485</v>
       </c>
       <c r="R8" t="n">
-        <v>487</v>
+        <v>998</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1192,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1295886962</t>
+          <t>1256642880</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1295886962</t>
+          <t>https://m.place.naver.com/place/1256642880</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>미녀와야수짐 안서점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>anseo1-1@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1333-6152</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충청남도 천안시 동남구 안서1길 1 젊은태양빌딩 3층 미녀와야수짐</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anseo1-1</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1251,15 +1283,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1271,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1486</v>
+        <v>126</v>
       </c>
       <c r="Q9" t="n">
-        <v>250</v>
+        <v>58</v>
       </c>
       <c r="R9" t="n">
-        <v>1736</v>
+        <v>184</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1286,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1036519698</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036519698</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FE트레이닝센터 천안점</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>edengarden0927@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1462-2471</t>
+          <t>0507-1378-6132</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 불당25로 236 디엠센텀시티 2층</t>
+          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/edengarden0927</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1350,13 +1386,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcsr94</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1365,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>256</v>
+        <v>167</v>
       </c>
       <c r="Q10" t="n">
-        <v>562</v>
+        <v>956</v>
       </c>
       <c r="R10" t="n">
-        <v>818</v>
+        <v>1123</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1380,51 +1420,47 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1149284242</t>
+          <t>1197800655</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1149284242</t>
+          <t>https://m.place.naver.com/place/1197800655</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>teamspartagym_@naver.com</t>
+          <t>hy_esoo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1378-6132</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1439,15 +1475,19 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5urik</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1459,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="Q11" t="n">
-        <v>948</v>
+        <v>327</v>
       </c>
       <c r="R11" t="n">
-        <v>1115</v>
+        <v>439</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1474,51 +1514,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1197800655</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197800655</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>크로스핏 트레이닝그라운드 SWEAT45 &amp; PT 불당점</t>
+          <t>리메이크짐 쌍용점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ddpwwf@naver.com</t>
+          <t>remakegym07@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1352-7077</t>
+          <t>0507-1378-0202</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>충청남도 천안시 서북구 불당4로 39-59 1F</t>
+          <t>충남 천안시 서북구 월봉로 92 4층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ddpwwf</t>
+          <t>https://www.instagram.com/remakegym</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1533,15 +1573,19 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5vaei</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1553,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>452</v>
+        <v>384</v>
       </c>
       <c r="Q12" t="n">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="R12" t="n">
-        <v>547</v>
+        <v>684</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1568,863 +1612,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1128230416</t>
+          <t>1287837862</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128230416</t>
+          <t>https://m.place.naver.com/place/1287837862</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>핏라이프피트니스 PT</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>fitlife-experts@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1333-1224</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 서북구 성성8로 2-44 바루나타워 6층, 핏라이프피트니스</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/fitlife-experts</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>620</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>1285</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1905</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>1310515227</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1310515227</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>천안 쌍용동 헬스&amp;PT 미녀와야수짐</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>dabinparks@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1309-2118</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 서북구 충무로 167-18 4층 미녀와야수짐 쌍용점</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/dabinparks</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>862</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>447</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1309</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1103877507</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1103877507</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>공감PT여성전용공간 성정동점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>djawndud99@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1344-6267</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 서북구 성정두정로 38 4층 401호</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://linktr.ee/gonggampt</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>46</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>160</v>
-      </c>
-      <c r="R15" t="n">
-        <v>206</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1159361767</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1159361767</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>하와이짐 직산점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>duddns20@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1484-8878</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 서북구 직산읍 직산로 43 4층 하와이짐</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/hawaiigym8877?igsh=eDdxcDRqZ3pjc2I5</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>235</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>152</v>
-      </c>
-      <c r="R16" t="n">
-        <v>387</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1303396625</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1303396625</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>핏러너 그룹PT 백석점</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>klsmys@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1324-7967</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 서북구 한들3로 85-48 1층 101호</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/klsmys</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>150</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>217</v>
-      </c>
-      <c r="R17" t="n">
-        <v>367</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1793060014</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1793060014</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>퓨처휘트니스 청당 헬스&amp;PT</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>futurefit@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1457-2391</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 동남구 청수14로 102 에이스법조타워 3층 301~309호</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/futurefit</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>923</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>816</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1739</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1704647072</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1704647072</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>지방부수리 24시 헬스&amp;PT 불당점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>kmgzxcv@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1344-7030</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 서북구 검은들1길 26 6층</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/kmgzxcv/223855885181</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>1538</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>483</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2021</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1012207514</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1012207514</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>온더짐 천안두정점 헬스 PT 필라테스</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>onthegym_official@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1390-0255</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 서북구 두정로 251 3층</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://youtube.com/channel/UCf8AIAmWKIKIzgNsS6vXaQg</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>151</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>307</v>
-      </c>
-      <c r="R20" t="n">
-        <v>458</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1233432048</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1233432048</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>오버핏스튜디오</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>overfit_studio@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1373-9636</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>충청남도 천안시 동남구 청수12로 44 301호</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/overfit_studio</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>56</v>
-      </c>
-      <c r="R21" t="n">
-        <v>72</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>2083680977</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2083680977</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -628,10 +628,10 @@
         <v>4146</v>
       </c>
       <c r="Q2" t="n">
-        <v>2964</v>
+        <v>2962</v>
       </c>
       <c r="R2" t="n">
-        <v>7110</v>
+        <v>7108</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q5" t="n">
         <v>58</v>
       </c>
       <c r="R5" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,25 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>미녀와야수짐 헬스&amp;PT 차암점</t>
+          <t>미녀와야수짐 안서점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>beauty_beast_gym@naver.com</t>
+          <t>anseo1-1@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1333-6152</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 3공단6로 58-8 천안비즈타워 307호~313호</t>
+          <t>충남 천안시 동남구 안서1길 1 젊은태양빌딩 3층 미녀와야수짐</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/beauty_beast_chaam?igsh=bmh0NW9vYWYxN2Vl</t>
+          <t>https://blog.naver.com/anseo1-1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1087,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1097,7 +1101,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zg2w</t>
+          <t>https://talk.naver.com/ct/w5zgjb</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1111,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>360</v>
+        <v>1482</v>
       </c>
       <c r="Q7" t="n">
-        <v>408</v>
+        <v>250</v>
       </c>
       <c r="R7" t="n">
-        <v>768</v>
+        <v>1732</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,51 +1130,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1965484568</t>
+          <t>1036519698</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965484568</t>
+          <t>https://m.place.naver.com/place/1036519698</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>365일 24시 짐그로우 쌍용역점</t>
+          <t>하루운동 PT&amp;헬스 천안두정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymgrow@naver.com</t>
+          <t>vhtm56@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1465-3657</t>
+          <t>0507-1368-1126</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
+          <t>충남 천안시 서북구 두정중2길 4 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymgrow/223761915716</t>
+          <t>https://blog.naver.com/vhtm56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w7k9</t>
+          <t>https://talk.naver.com/ct/w4r6u6</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>513</v>
+        <v>201</v>
       </c>
       <c r="Q8" t="n">
-        <v>485</v>
+        <v>112</v>
       </c>
       <c r="R8" t="n">
-        <v>998</v>
+        <v>313</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1256642880</t>
+          <t>1043441965</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256642880</t>
+          <t>https://m.place.naver.com/place/1043441965</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>365일 24시 짐그로우 쌍용역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>gymgrow@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1309-9270</t>
+          <t>0507-1465-3657</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/gymgrow/223761915716</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1287,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/w5w7k9</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>126</v>
+        <v>514</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>486</v>
       </c>
       <c r="R9" t="n">
-        <v>184</v>
+        <v>1000</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1326,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1256642880</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1256642880</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>teamspartagym_@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1378-6132</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,12 +1395,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsr94</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="Q10" t="n">
-        <v>956</v>
+        <v>58</v>
       </c>
       <c r="R10" t="n">
-        <v>1123</v>
+        <v>185</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,47 +1424,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1197800655</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197800655</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hy_esoo@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1344-6267</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://linktr.ee/gonggampt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1483,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,12 +1493,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/w4ls51</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1507,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>112</v>
+        <v>46</v>
       </c>
       <c r="Q11" t="n">
-        <v>327</v>
+        <v>162</v>
       </c>
       <c r="R11" t="n">
-        <v>439</v>
+        <v>208</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,115 +1522,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>1159361767</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>리메이크짐 쌍용점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>remakegym07@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1378-0202</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>충남 천안시 서북구 월봉로 92 4층</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/remakegym</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5vaei</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>384</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>300</v>
-      </c>
-      <c r="R12" t="n">
-        <v>684</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1287837862</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1287837862</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="Q7" t="n">
         <v>250</v>
       </c>
       <c r="R7" t="n">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1531,6 +1531,100 @@
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>함마짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>soyoung_lee1@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5urik</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>110</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>327</v>
+      </c>
+      <c r="R12" t="n">
+        <v>437</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1163060455</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1163060455</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -421,7 +421,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
     <col width="28" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
@@ -628,10 +628,10 @@
         <v>4146</v>
       </c>
       <c r="Q2" t="n">
-        <v>2962</v>
+        <v>2960</v>
       </c>
       <c r="R2" t="n">
-        <v>7108</v>
+        <v>7106</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -824,10 +824,10 @@
         <v>924</v>
       </c>
       <c r="Q4" t="n">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="R4" t="n">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>크로스핏 트레이닝그라운드 SWEAT45 &amp; PT 불당점</t>
+          <t>미녀와야수짐 안서점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ddpwwf@naver.com</t>
+          <t>anseo1-1@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1352-7077</t>
+          <t>0507-1333-6152</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당4로 39-59 1F</t>
+          <t>충남 천안시 동남구 안서1길 1 젊은태양빌딩 3층 미녀와야수짐</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ddpwwf</t>
+          <t>https://blog.naver.com/anseo1-1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w43u70</t>
+          <t>https://talk.naver.com/ct/w5zgjb</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>455</v>
+        <v>1483</v>
       </c>
       <c r="Q6" t="n">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="R6" t="n">
-        <v>550</v>
+        <v>1733</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1128230416</t>
+          <t>1036519698</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1128230416</t>
+          <t>https://m.place.naver.com/place/1036519698</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1054,29 +1054,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>미녀와야수짐 안서점</t>
+          <t>미녀와야수짐 헬스&amp;PT 차암점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>anseo1-1@naver.com</t>
+          <t>beauty_beast_gym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1333-6152</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 안서1길 1 젊은태양빌딩 3층 미녀와야수짐</t>
+          <t>충남 천안시 서북구 3공단6로 58-8 천안비즈타워 307호~313호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anseo1-1</t>
+          <t>https://www.instagram.com/beauty_beast_chaam?igsh=bmh0NW9vYWYxN2Vl</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1087,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,7 +1097,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zgjb</t>
+          <t>https://talk.naver.com/ct/w5zg2w</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1115,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1481</v>
+        <v>360</v>
       </c>
       <c r="Q7" t="n">
-        <v>250</v>
+        <v>408</v>
       </c>
       <c r="R7" t="n">
-        <v>1731</v>
+        <v>768</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1036519698</t>
+          <t>1965484568</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036519698</t>
+          <t>https://m.place.naver.com/place/1965484568</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1147,34 +1143,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하루운동 PT&amp;헬스 천안두정점</t>
+          <t>365일 24시 짐그로우 쌍용역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vhtm56@naver.com</t>
+          <t>gymgrow@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1368-1126</t>
+          <t>0507-1465-3657</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정중2길 4 4층</t>
+          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vhtm56</t>
+          <t>https://blog.naver.com/gymgrow/223761915716</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r6u6</t>
+          <t>https://talk.naver.com/ct/w5w7k9</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>201</v>
+        <v>514</v>
       </c>
       <c r="Q8" t="n">
-        <v>112</v>
+        <v>486</v>
       </c>
       <c r="R8" t="n">
-        <v>313</v>
+        <v>1000</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1043441965</t>
+          <t>1256642880</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043441965</t>
+          <t>https://m.place.naver.com/place/1256642880</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,34 +1241,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>365일 24시 짐그로우 쌍용역점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymgrow@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1465-3657</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymgrow/223761915716</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w7k9</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>514</v>
+        <v>127</v>
       </c>
       <c r="Q9" t="n">
-        <v>486</v>
+        <v>58</v>
       </c>
       <c r="R9" t="n">
-        <v>1000</v>
+        <v>185</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1256642880</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256642880</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1348,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1309-9270</t>
+          <t>0507-1378-6132</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1385,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1395,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/wcsr94</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="Q10" t="n">
-        <v>58</v>
+        <v>957</v>
       </c>
       <c r="R10" t="n">
-        <v>185</v>
+        <v>1124</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1197800655</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1197800655</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4146</v>
+        <v>4144</v>
       </c>
       <c r="Q2" t="n">
         <v>2960</v>
       </c>
       <c r="R2" t="n">
-        <v>7106</v>
+        <v>7104</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>414</v>
       </c>
       <c r="Q3" t="n">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="R3" t="n">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -1020,10 +1020,10 @@
         <v>1483</v>
       </c>
       <c r="Q6" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="R6" t="n">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1212,10 +1212,10 @@
         <v>514</v>
       </c>
       <c r="Q8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="R8" t="n">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1344,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>teamspartagym_@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1378-6132</t>
+          <t>0507-1344-6267</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
+          <t>https://linktr.ee/gonggampt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcsr94</t>
+          <t>https://talk.naver.com/ct/w4ls51</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>167</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>957</v>
+        <v>162</v>
       </c>
       <c r="R10" t="n">
-        <v>1124</v>
+        <v>208</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1197800655</t>
+          <t>1159361767</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1197800655</t>
+          <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,34 +1437,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공감PT여성전용공간 성정동점</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>djawndud99@naver.com</t>
+          <t>soyoung_lee1@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1344-6267</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggampt</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ls51</t>
+          <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="Q11" t="n">
-        <v>162</v>
+        <v>327</v>
       </c>
       <c r="R11" t="n">
-        <v>208</v>
+        <v>437</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,12 +1514,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1159361767</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159361767</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1535,35 +1531,39 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>필라테스 스코프</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>soyoung_lee1@naver.com</t>
+          <t>pilates_scope@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1391-8966</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 불당22대로 86 402호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://pf.kakao.com/_xnxlkmn/chat</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1583,12 +1583,12 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/wuqiv1k</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -1597,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="Q12" t="n">
-        <v>327</v>
+        <v>25</v>
       </c>
       <c r="R12" t="n">
-        <v>437</v>
+        <v>48</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>2023921054</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/2023921054</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q3" t="n">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="R3" t="n">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -824,10 +824,10 @@
         <v>924</v>
       </c>
       <c r="Q4" t="n">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="R4" t="n">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -922,10 +922,10 @@
         <v>13</v>
       </c>
       <c r="Q5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1136,41 +1136,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>365일 24시 짐그로우 쌍용역점</t>
+          <t>하루운동 PT&amp;헬스 천안두정점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>gymgrow@naver.com</t>
+          <t>vhtm56@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1465-3657</t>
+          <t>0507-1368-1126</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
+          <t>충남 천안시 서북구 두정중2길 4 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymgrow/223761915716</t>
+          <t>https://blog.naver.com/vhtm56</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w7k9</t>
+          <t>https://talk.naver.com/ct/w4r6u6</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1209,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>514</v>
+        <v>201</v>
       </c>
       <c r="Q8" t="n">
-        <v>487</v>
+        <v>112</v>
       </c>
       <c r="R8" t="n">
-        <v>1001</v>
+        <v>313</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1256642880</t>
+          <t>1043441965</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256642880</t>
+          <t>https://m.place.naver.com/place/1043441965</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>365일 24시 짐그로우 쌍용역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>gymgrow@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1309-9270</t>
+          <t>0507-1465-3657</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/gymgrow/223761915716</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/w5w7k9</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>127</v>
+        <v>514</v>
       </c>
       <c r="Q9" t="n">
-        <v>58</v>
+        <v>487</v>
       </c>
       <c r="R9" t="n">
-        <v>185</v>
+        <v>1001</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1322,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1256642880</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1256642880</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1344,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공감PT여성전용공간 성정동점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>djawndud99@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1344-6267</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggampt</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ls51</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="Q10" t="n">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="R10" t="n">
-        <v>208</v>
+        <v>185</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,47 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1159361767</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159361767</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>soyoung_lee1@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1378-6132</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,12 +1489,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/wcsr94</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>110</v>
+        <v>167</v>
       </c>
       <c r="Q11" t="n">
-        <v>327</v>
+        <v>957</v>
       </c>
       <c r="R11" t="n">
-        <v>437</v>
+        <v>1124</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,56 +1518,56 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>1197800655</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/1197800655</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>필라테스 스코프</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>pilates_scope@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1391-8966</t>
+          <t>0507-1344-6267</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당22대로 86 402호</t>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnxlkmn/chat</t>
+          <t>https://linktr.ee/gonggampt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1573,7 +1577,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1583,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuqiv1k</t>
+          <t>https://talk.naver.com/ct/w4ls51</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="Q12" t="n">
-        <v>25</v>
+        <v>162</v>
       </c>
       <c r="R12" t="n">
-        <v>48</v>
+        <v>208</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,17 +1616,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2023921054</t>
+          <t>1159361767</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023921054</t>
+          <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -628,10 +628,10 @@
         <v>4144</v>
       </c>
       <c r="Q2" t="n">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="R2" t="n">
-        <v>7104</v>
+        <v>7103</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -726,10 +726,10 @@
         <v>415</v>
       </c>
       <c r="Q3" t="n">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="R3" t="n">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -760,29 +760,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>퓨처휘트니스 성성점 헬스&amp;PT</t>
+          <t>미녀와야수짐 안서점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>futurefit_ss@naver.com</t>
+          <t>anseo1-1@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1330-3335</t>
+          <t>0507-1333-6152</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성성5로 113 B1층</t>
+          <t>충남 천안시 동남구 안서1길 1 젊은태양빌딩 3층 미녀와야수짐</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/futurefit_ss</t>
+          <t>https://blog.naver.com/anseo1-1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w489t7</t>
+          <t>https://talk.naver.com/ct/w5zgjb</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>924</v>
+        <v>1483</v>
       </c>
       <c r="Q4" t="n">
-        <v>841</v>
+        <v>251</v>
       </c>
       <c r="R4" t="n">
-        <v>1765</v>
+        <v>1734</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1174227079</t>
+          <t>1036519698</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1174227079</t>
+          <t>https://m.place.naver.com/place/1036519698</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -858,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>오버핏스튜디오</t>
+          <t>퓨처휘트니스 성성점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>overfit_studio@naver.com</t>
+          <t>futurefit_ss@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1373-9636</t>
+          <t>0507-1330-3335</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수12로 44 301호</t>
+          <t>충남 천안시 서북구 성성5로 113 B1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/overfit_studio</t>
+          <t>https://blog.naver.com/futurefit_ss</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcs5xy4</t>
+          <t>https://talk.naver.com/ct/w489t7</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>13</v>
+        <v>924</v>
       </c>
       <c r="Q5" t="n">
-        <v>59</v>
+        <v>841</v>
       </c>
       <c r="R5" t="n">
-        <v>72</v>
+        <v>1765</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2083680977</t>
+          <t>1174227079</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2083680977</t>
+          <t>https://m.place.naver.com/place/1174227079</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -956,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>미녀와야수짐 안서점</t>
+          <t>오버핏스튜디오</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>anseo1-1@naver.com</t>
+          <t>overfit_studio@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1333-6152</t>
+          <t>0507-1373-9636</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 안서1길 1 젊은태양빌딩 3층 미녀와야수짐</t>
+          <t>충남 천안시 동남구 청수12로 44 301호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/anseo1-1</t>
+          <t>https://blog.naver.com/overfit_studio</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5zgjb</t>
+          <t>https://talk.naver.com/ct/wcs5xy4</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1483</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>251</v>
+        <v>59</v>
       </c>
       <c r="R6" t="n">
-        <v>1734</v>
+        <v>72</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1036519698</t>
+          <t>2083680977</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1036519698</t>
+          <t>https://m.place.naver.com/place/2083680977</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>하루운동 PT&amp;헬스 천안두정점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>vhtm56@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1368-1126</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정중2길 4 4층</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/vhtm56</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4r6u6</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>201</v>
+        <v>128</v>
       </c>
       <c r="Q8" t="n">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="R8" t="n">
-        <v>313</v>
+        <v>187</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1043441965</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043441965</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1245,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>365일 24시 짐그로우 쌍용역점</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>gymgrow@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1465-3657</t>
+          <t>0507-1344-6267</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/gymgrow/223761915716</t>
+          <t>https://linktr.ee/gonggampt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,12 +1297,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w7k9</t>
+          <t>https://talk.naver.com/ct/w4ls51</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>515</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="n">
-        <v>488</v>
+        <v>162</v>
       </c>
       <c r="R9" t="n">
-        <v>1003</v>
+        <v>208</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1256642880</t>
+          <t>1159361767</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1256642880</t>
+          <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1343,34 +1343,30 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>hy_esoo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0507-1309-9270</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1395,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1409,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="Q10" t="n">
-        <v>59</v>
+        <v>327</v>
       </c>
       <c r="R10" t="n">
-        <v>187</v>
+        <v>437</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1424,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1441,39 +1437,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>필라테스</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공감PT여성전용공간 성정동점</t>
+          <t>필라테스 스코프</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>djawndud99@naver.com</t>
+          <t>pilates_scope@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1344-6267</t>
+          <t>0507-1391-8966</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충남 천안시 서북구 불당22대로 86 402호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggampt</t>
+          <t>https://pf.kakao.com/_xnxlkmn/chat</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1483,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1493,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ls51</t>
+          <t>https://talk.naver.com/ct/wuqiv1k</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1507,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="R11" t="n">
-        <v>208</v>
+        <v>49</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1522,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1159361767</t>
+          <t>2023921054</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159361767</t>
+          <t>https://m.place.naver.com/place/2023921054</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="Q2" t="n">
         <v>2959</v>
       </c>
       <c r="R2" t="n">
-        <v>7103</v>
+        <v>7104</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -704,14 +704,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wsb8r4z</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -748,7 +744,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +842,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -944,7 +940,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1038,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1140,41 +1136,41 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>유어짐 청당점</t>
+          <t>365일 24시 짐그로우 쌍용역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>your_gym@naver.com</t>
+          <t>gymgrow@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1309-9270</t>
+          <t>0507-1465-3657</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
+          <t>충남 천안시 서북구 충무로 155 2층 짐그로우</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
+          <t>https://blog.naver.com/gymgrow/223761915716</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1189,7 +1185,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1199,7 +1195,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wepzfrf</t>
+          <t>https://talk.naver.com/ct/w5w7k9</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>128</v>
+        <v>516</v>
       </c>
       <c r="Q8" t="n">
-        <v>59</v>
+        <v>488</v>
       </c>
       <c r="R8" t="n">
-        <v>187</v>
+        <v>1004</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,17 +1224,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2055460977</t>
+          <t>1256642880</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055460977</t>
+          <t>https://m.place.naver.com/place/1256642880</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1246,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>공감PT여성전용공간 성정동점</t>
+          <t>유어짐 청당점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>djawndud99@naver.com</t>
+          <t>your_gym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1344-6267</t>
+          <t>0507-1309-9270</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충남 천안시 동남구 청수11로 16 901호, 902호, 903호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggampt</t>
+          <t>https://www.instagram.com/your_gym_cd?igsh=NXMyOWVzdWFodHJw&amp;utm_source=qr</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1287,7 +1283,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1297,12 +1293,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ls51</t>
+          <t>https://talk.naver.com/ct/wepzfrf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1311,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="Q9" t="n">
-        <v>162</v>
+        <v>59</v>
       </c>
       <c r="R9" t="n">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,47 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1159361767</t>
+          <t>2055460977</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159361767</t>
+          <t>https://m.place.naver.com/place/2055460977</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hy_esoo@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0507-1344-6267</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 두정로 166 4층</t>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/gym_hammar_boss</t>
+          <t>https://linktr.ee/gonggampt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1381,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,12 +1391,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5urik</t>
+          <t>https://talk.naver.com/ct/w4ls51</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="Q10" t="n">
-        <v>327</v>
+        <v>162</v>
       </c>
       <c r="R10" t="n">
-        <v>437</v>
+        <v>208</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,56 +1420,52 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1163060455</t>
+          <t>1159361767</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1163060455</t>
+          <t>https://m.place.naver.com/place/1159361767</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>필라테스</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>필라테스 스코프</t>
+          <t>함마짐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>pilates_scope@naver.com</t>
+          <t>hy_esoo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0507-1391-8966</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 불당22대로 86 402호</t>
+          <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://pf.kakao.com/_xnxlkmn/chat</t>
+          <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1489,12 +1485,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wuqiv1k</t>
+          <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>327</v>
       </c>
       <c r="R11" t="n">
-        <v>49</v>
+        <v>437</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,17 +1514,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2023921054</t>
+          <t>1163060455</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2023921054</t>
+          <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/천안_PT.xlsx
+++ b/naver-place-crawler/results_health/천안_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -704,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wsb8r4z</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -1016,10 +1020,10 @@
         <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R6" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1344,29 +1348,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공감PT여성전용공간 성정동점</t>
+          <t>성정동PT 팀스파르타짐 헬스&amp;PT 성정점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>djawndud99@naver.com</t>
+          <t>teamspartagym_@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1344-6267</t>
+          <t>0507-1378-6132</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+          <t>충남 천안시 서북구 동서대로 117 펜모아 3층 팀스파르타짐 성정점</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://linktr.ee/gonggampt</t>
+          <t>https://blog.naver.com/teamspartagym_/223877797520</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1391,7 +1395,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4ls51</t>
+          <t>https://talk.naver.com/ct/wcsr94</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1405,13 +1409,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>46</v>
+        <v>167</v>
       </c>
       <c r="Q10" t="n">
-        <v>162</v>
+        <v>959</v>
       </c>
       <c r="R10" t="n">
-        <v>208</v>
+        <v>1126</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,12 +1424,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1159361767</t>
+          <t>1197800655</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1159361767</t>
+          <t>https://m.place.naver.com/place/1197800655</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1437,92 +1441,190 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>함마짐</t>
+          <t>공감PT여성전용공간 성정동점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hy_esoo@naver.com</t>
+          <t>djawndud99@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0507-1344-6267</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
+          <t>충남 천안시 서북구 성정두정로 38 4층 401호</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>https://linktr.ee/gonggampt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ls51</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>46</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>162</v>
+      </c>
+      <c r="R11" t="n">
+        <v>208</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1159361767</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1159361767</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>함마짐</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hy_esoo@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>충남 천안시 서북구 두정로 166 4층</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>https://www.instagram.com/gym_hammar_boss</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>https://talk.naver.com/ct/w5urik</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P11" t="n">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
         <v>110</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" t="n">
         <v>327</v>
       </c>
-      <c r="R11" t="n">
+      <c r="R12" t="n">
         <v>437</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>1163060455</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1163060455</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
